--- a/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0003T0006Z000C1N9_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0003T0006Z000C1N9_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>32.84925957879848</v>
+        <v>5.338004681554754</v>
       </c>
       <c r="D2" t="n">
-        <v>34.21435911037072</v>
+        <v>5.559833355435241</v>
       </c>
       <c r="E2" t="n">
-        <v>5.49252116209265</v>
+        <v>0.8925346888400557</v>
       </c>
       <c r="F2" t="n">
-        <v>10.18062853062689</v>
+        <v>1.65435213622687</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.67631735820172</v>
+        <v>5.63490157070778</v>
       </c>
       <c r="D3" t="n">
-        <v>35.27921860196158</v>
+        <v>5.732873022818757</v>
       </c>
       <c r="E3" t="n">
-        <v>5.49252116209265</v>
+        <v>0.8925346888400557</v>
       </c>
       <c r="F3" t="n">
-        <v>10.18062853062689</v>
+        <v>1.65435213622687</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.90451097128898</v>
+        <v>4.04698303283446</v>
       </c>
       <c r="D4" t="n">
-        <v>24.71725711803827</v>
+        <v>4.016554281681218</v>
       </c>
       <c r="E4" t="n">
-        <v>5.49252116209265</v>
+        <v>0.8925346888400557</v>
       </c>
       <c r="F4" t="n">
-        <v>10.18062853062689</v>
+        <v>1.65435213622687</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>31.14586749972359</v>
+        <v>5.061203468705084</v>
       </c>
       <c r="D5" t="n">
-        <v>30.96651238113699</v>
+        <v>5.03205826193476</v>
       </c>
       <c r="E5" t="n">
-        <v>5.49252116209265</v>
+        <v>0.8925346888400557</v>
       </c>
       <c r="F5" t="n">
-        <v>10.18062853062689</v>
+        <v>1.65435213622687</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>15.47700424186436</v>
+        <v>2.515013189302959</v>
       </c>
       <c r="D6" t="n">
-        <v>15.32964014255029</v>
+        <v>2.491066523164422</v>
       </c>
       <c r="E6" t="n">
-        <v>5.49252116209265</v>
+        <v>0.8925346888400557</v>
       </c>
       <c r="F6" t="n">
-        <v>10.18062853062689</v>
+        <v>1.65435213622687</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>26.59909862430179</v>
+        <v>4.322353526449041</v>
       </c>
       <c r="D7" t="n">
-        <v>26.77844539110786</v>
+        <v>4.351497376055027</v>
       </c>
       <c r="E7" t="n">
-        <v>5.49252116209265</v>
+        <v>0.8925346888400557</v>
       </c>
       <c r="F7" t="n">
-        <v>10.18062853062689</v>
+        <v>1.65435213622687</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>25.32450272033554</v>
+        <v>4.115231692054525</v>
       </c>
       <c r="D8" t="n">
-        <v>38.32371908688633</v>
+        <v>6.227604351619028</v>
       </c>
       <c r="E8" t="n">
-        <v>5.49252116209265</v>
+        <v>0.8925346888400557</v>
       </c>
       <c r="F8" t="n">
-        <v>10.18062853062689</v>
+        <v>1.65435213622687</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>22.66945822696049</v>
+        <v>3.68378696188108</v>
       </c>
       <c r="D9" t="n">
-        <v>33.00709330068815</v>
+        <v>5.363652661361825</v>
       </c>
       <c r="E9" t="n">
-        <v>5.49252116209265</v>
+        <v>0.8925346888400557</v>
       </c>
       <c r="F9" t="n">
-        <v>10.18062853062689</v>
+        <v>1.65435213622687</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>24.87392813883142</v>
+        <v>4.042013322560106</v>
       </c>
       <c r="D10" t="n">
-        <v>54.80662144486957</v>
+        <v>8.906075984791306</v>
       </c>
       <c r="E10" t="n">
-        <v>5.49252116209265</v>
+        <v>0.8925346888400557</v>
       </c>
       <c r="F10" t="n">
-        <v>10.18062853062689</v>
+        <v>1.65435213622687</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
